--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/MICHIGAN_2012.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/MICHIGAN_2012.xlsx
@@ -1518,7 +1518,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C65">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C122">
@@ -9204,7 +9204,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C492">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C554">
@@ -14100,7 +14100,7 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C764">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C858">
